--- a/12603165.xlsx
+++ b/12603165.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ujjwa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{76DCAEC3-1376-47B9-9155-63B345E19B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DD0871E-E9E5-4041-939E-5D726BAD2126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -194,31 +193,40 @@
     <t>MCA D1P2632</t>
   </si>
   <si>
-    <t>Fantastic</t>
-  </si>
-  <si>
     <t>High</t>
   </si>
   <si>
-    <t>Attended and Amazing Concert in the evening.</t>
-  </si>
-  <si>
-    <t>Energatic</t>
-  </si>
-  <si>
     <t>AUGUST</t>
-  </si>
-  <si>
-    <t>Hectic</t>
-  </si>
-  <si>
-    <t>Normal</t>
   </si>
   <si>
     <t>Felt tired  after attending classes.</t>
   </si>
   <si>
     <t>Day was very sunny .</t>
+  </si>
+  <si>
+    <t>Attended an Amazing Concert in the evening.</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Satisfied</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Enjoyed a day off after 5 day full of classes and stress.</t>
   </si>
 </sst>
 </file>
@@ -909,7 +917,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G3" s="15"/>
     </row>
@@ -1009,16 +1017,16 @@
         <v>140</v>
       </c>
       <c r="K6" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N6" s="12" t="s">
         <v>56</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="N6" s="12" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -1055,16 +1063,16 @@
         <v>10</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="M7" s="11" t="s">
         <v>49</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -1101,61 +1109,109 @@
         <v>380</v>
       </c>
       <c r="K8" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="M8" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="L8" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>54</v>
-      </c>
       <c r="N8" s="12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="10" t="str">
+      <c r="A9" s="8">
+        <v>46255</v>
+      </c>
+      <c r="B9" s="9">
+        <v>250</v>
+      </c>
+      <c r="C9" s="9">
+        <v>40</v>
+      </c>
+      <c r="D9" s="9">
+        <v>150</v>
+      </c>
+      <c r="E9" s="9">
+        <v>60</v>
+      </c>
+      <c r="F9" s="9">
+        <v>480</v>
+      </c>
+      <c r="G9" s="9">
+        <v>7</v>
+      </c>
+      <c r="H9" s="9">
+        <v>190</v>
+      </c>
+      <c r="I9" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="10" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J9" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="12"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="10" t="str">
+        <v>270</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N9" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="8">
+        <v>46256</v>
+      </c>
+      <c r="B10" s="9">
+        <v>310</v>
+      </c>
+      <c r="C10" s="9">
+        <v>0</v>
+      </c>
+      <c r="D10" s="9">
+        <v>390</v>
+      </c>
+      <c r="E10" s="9">
+        <v>120</v>
+      </c>
+      <c r="F10" s="9">
+        <v>0</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>480</v>
+      </c>
+      <c r="I10" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="10" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J10" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="12"/>
+        <v>140</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N10" s="12" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>

--- a/12603165.xlsx
+++ b/12603165.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ujjwa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DD0871E-E9E5-4041-939E-5D726BAD2126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9952EC35-A544-425D-BD74-0E67385421E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -227,6 +227,18 @@
   </si>
   <si>
     <t>Enjoyed a day off after 5 day full of classes and stress.</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Watched 2 fantastic documentries , on data centers being setup .</t>
+  </si>
+  <si>
+    <t>Attendent first Advance Communication class.</t>
+  </si>
+  <si>
+    <t>Solved Sandbox problems</t>
   </si>
 </sst>
 </file>
@@ -1213,71 +1225,143 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="10" t="str">
+    <row r="11" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="8">
+        <v>46257</v>
+      </c>
+      <c r="B11" s="9">
+        <v>240</v>
+      </c>
+      <c r="C11" s="9">
+        <v>40</v>
+      </c>
+      <c r="D11" s="9">
+        <v>100</v>
+      </c>
+      <c r="E11" s="9">
+        <v>30</v>
+      </c>
+      <c r="F11" s="9">
+        <v>0</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0</v>
+      </c>
+      <c r="H11" s="9">
+        <v>600</v>
+      </c>
+      <c r="I11" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="10" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J11" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="12"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="10" t="str">
+        <v>430</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N11" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B12" s="9">
+        <v>360</v>
+      </c>
+      <c r="C12" s="9">
+        <v>20</v>
+      </c>
+      <c r="D12" s="9">
+        <v>120</v>
+      </c>
+      <c r="E12" s="9">
+        <v>60</v>
+      </c>
+      <c r="F12" s="9">
+        <v>420</v>
+      </c>
+      <c r="G12" s="9">
+        <v>7</v>
+      </c>
+      <c r="H12" s="9">
+        <v>200</v>
+      </c>
+      <c r="I12" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="10" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J12" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="12"/>
+        <v>260</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="12" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="10" t="str">
+      <c r="A13" s="8">
+        <v>46259</v>
+      </c>
+      <c r="B13" s="9">
+        <v>160</v>
+      </c>
+      <c r="C13" s="9">
+        <v>40</v>
+      </c>
+      <c r="D13" s="9">
+        <v>300</v>
+      </c>
+      <c r="E13" s="9">
+        <v>60</v>
+      </c>
+      <c r="F13" s="9">
+        <v>180</v>
+      </c>
+      <c r="G13" s="9">
+        <v>3</v>
+      </c>
+      <c r="H13" s="9">
+        <v>460</v>
+      </c>
+      <c r="I13" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="10" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J13" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="12"/>
+        <v>240</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>

--- a/12603165.xlsx
+++ b/12603165.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ujjwa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9952EC35-A544-425D-BD74-0E67385421E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF6AD87-8628-4FC9-AFF8-7DF1EC10B8CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t>Solved Sandbox problems</t>
+  </si>
+  <si>
+    <t>Gave practice test for Analytical skills.</t>
   </si>
 </sst>
 </file>
@@ -1363,27 +1366,51 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="10" t="str">
+    <row r="14" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="8">
+        <v>46260</v>
+      </c>
+      <c r="B14" s="9">
+        <v>270</v>
+      </c>
+      <c r="C14" s="9">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9">
+        <v>80</v>
+      </c>
+      <c r="E14" s="9">
+        <v>60</v>
+      </c>
+      <c r="F14" s="9">
+        <v>420</v>
+      </c>
+      <c r="G14" s="9">
+        <v>7</v>
+      </c>
+      <c r="H14" s="9">
+        <v>150</v>
+      </c>
+      <c r="I14" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="10" t="str">
+        <v>980</v>
+      </c>
+      <c r="J14" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="12"/>
+        <v>460</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N14" s="12" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>

--- a/12603165.xlsx
+++ b/12603165.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ujjwa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF6AD87-8628-4FC9-AFF8-7DF1EC10B8CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C86C96-DD72-4EC0-B34C-F7B44E9660BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -242,6 +242,12 @@
   </si>
   <si>
     <t>Gave practice test for Analytical skills.</t>
+  </si>
+  <si>
+    <t>Had an amazing tme solving questions .</t>
+  </si>
+  <si>
+    <t>Celebated the festival of Rakhi. And Talked to all my cousins.</t>
   </si>
 </sst>
 </file>
@@ -1383,21 +1389,21 @@
         <v>60</v>
       </c>
       <c r="F14" s="9">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="G14" s="9">
         <v>7</v>
       </c>
       <c r="H14" s="9">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="I14" s="10">
         <f t="shared" si="0"/>
-        <v>980</v>
+        <v>960</v>
       </c>
       <c r="J14" s="10">
         <f t="shared" si="1"/>
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>61</v>
@@ -1412,49 +1418,97 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="10" t="str">
+    <row r="15" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="8">
+        <v>46261</v>
+      </c>
+      <c r="B15" s="9">
+        <v>360</v>
+      </c>
+      <c r="C15" s="9">
+        <v>40</v>
+      </c>
+      <c r="D15" s="9">
+        <v>140</v>
+      </c>
+      <c r="E15" s="9">
+        <v>55</v>
+      </c>
+      <c r="F15" s="9">
+        <v>200</v>
+      </c>
+      <c r="G15" s="9">
+        <v>4</v>
+      </c>
+      <c r="H15" s="9">
+        <v>300</v>
+      </c>
+      <c r="I15" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="10" t="str">
+        <v>1095</v>
+      </c>
+      <c r="J15" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="12"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="10" t="str">
+        <v>345</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N15" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="8">
+        <v>46262</v>
+      </c>
+      <c r="B16" s="9">
+        <v>400</v>
+      </c>
+      <c r="C16" s="9">
+        <v>45</v>
+      </c>
+      <c r="D16" s="9">
+        <v>120</v>
+      </c>
+      <c r="E16" s="9">
+        <v>75</v>
+      </c>
+      <c r="F16" s="9">
+        <v>250</v>
+      </c>
+      <c r="G16" s="9">
+        <v>5</v>
+      </c>
+      <c r="H16" s="9">
+        <v>450</v>
+      </c>
+      <c r="I16" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="10" t="str">
+        <v>1340</v>
+      </c>
+      <c r="J16" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="12"/>
+        <v>100</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="8"/>

--- a/12603165.xlsx
+++ b/12603165.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ujjwa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C86C96-DD72-4EC0-B34C-F7B44E9660BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F428A950-8D6D-423D-9FCA-AF5CB96CED02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -248,6 +248,12 @@
   </si>
   <si>
     <t>Celebated the festival of Rakhi. And Talked to all my cousins.</t>
+  </si>
+  <si>
+    <t>Completed my freelance work of Website UI design For a jewellery brand.</t>
+  </si>
+  <si>
+    <t>day was boring.</t>
   </si>
 </sst>
 </file>
@@ -1510,49 +1516,97 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="10" t="str">
+    <row r="17" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A17" s="8">
+        <v>46263</v>
+      </c>
+      <c r="B17" s="9">
+        <v>480</v>
+      </c>
+      <c r="C17" s="9">
+        <v>45</v>
+      </c>
+      <c r="D17" s="9">
+        <v>250</v>
+      </c>
+      <c r="E17" s="9">
+        <v>60</v>
+      </c>
+      <c r="F17" s="9">
+        <v>0</v>
+      </c>
+      <c r="G17" s="9">
+        <v>0</v>
+      </c>
+      <c r="H17" s="9">
+        <v>600</v>
+      </c>
+      <c r="I17" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="10" t="str">
+        <v>1435</v>
+      </c>
+      <c r="J17" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="12"/>
+        <v>5</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N17" s="12" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="10" t="str">
+      <c r="A18" s="8">
+        <v>46264</v>
+      </c>
+      <c r="B18" s="9">
+        <v>340</v>
+      </c>
+      <c r="C18" s="9">
+        <v>30</v>
+      </c>
+      <c r="D18" s="9">
+        <v>300</v>
+      </c>
+      <c r="E18" s="9">
+        <v>110</v>
+      </c>
+      <c r="F18" s="9">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>480</v>
+      </c>
+      <c r="I18" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="10" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J18" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="12"/>
+        <v>180</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N18" s="12" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="8"/>

--- a/12603165.xlsx
+++ b/12603165.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ujjwa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F428A950-8D6D-423D-9FCA-AF5CB96CED02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78E87F45-C6E4-4B97-9C42-D8B8E8DD8CC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -254,6 +254,18 @@
   </si>
   <si>
     <t>day was boring.</t>
+  </si>
+  <si>
+    <t>Day started as very good but was tired till the end.</t>
+  </si>
+  <si>
+    <t>Recorded a Introduction video .</t>
+  </si>
+  <si>
+    <t>Day was very tiring.</t>
+  </si>
+  <si>
+    <t>Edited few montage videos.</t>
   </si>
 </sst>
 </file>
@@ -1608,93 +1620,189 @@
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="10" t="str">
+    <row r="19" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B19" s="9">
+        <v>280</v>
+      </c>
+      <c r="C19" s="9">
+        <v>45</v>
+      </c>
+      <c r="D19" s="9">
+        <v>200</v>
+      </c>
+      <c r="E19" s="9">
+        <v>70</v>
+      </c>
+      <c r="F19" s="9">
+        <v>350</v>
+      </c>
+      <c r="G19" s="9">
+        <v>7</v>
+      </c>
+      <c r="H19" s="9">
+        <v>245</v>
+      </c>
+      <c r="I19" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="10" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J19" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="12"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="10" t="str">
+        <v>250</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N19" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B20" s="9">
+        <v>370</v>
+      </c>
+      <c r="C20" s="9">
+        <v>40</v>
+      </c>
+      <c r="D20" s="9">
+        <v>160</v>
+      </c>
+      <c r="E20" s="9">
+        <v>150</v>
+      </c>
+      <c r="F20" s="9">
+        <v>150</v>
+      </c>
+      <c r="G20" s="9">
+        <v>3</v>
+      </c>
+      <c r="H20" s="9">
+        <v>160</v>
+      </c>
+      <c r="I20" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="10" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J20" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="12"/>
+        <v>410</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L20" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N20" s="12" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="10" t="str">
+      <c r="A21" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B21" s="9">
+        <v>310</v>
+      </c>
+      <c r="C21" s="9">
+        <v>45</v>
+      </c>
+      <c r="D21" s="9">
+        <v>160</v>
+      </c>
+      <c r="E21" s="9">
+        <v>100</v>
+      </c>
+      <c r="F21" s="9">
+        <v>400</v>
+      </c>
+      <c r="G21" s="9">
+        <v>8</v>
+      </c>
+      <c r="H21" s="9">
+        <v>220</v>
+      </c>
+      <c r="I21" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="10" t="str">
+        <v>1235</v>
+      </c>
+      <c r="J21" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="12"/>
+        <v>205</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L21" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="N21" s="12" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="10" t="str">
+      <c r="A22" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B22" s="9">
+        <v>290</v>
+      </c>
+      <c r="C22" s="9">
+        <v>45</v>
+      </c>
+      <c r="D22" s="9">
+        <v>180</v>
+      </c>
+      <c r="E22" s="9">
+        <v>100</v>
+      </c>
+      <c r="F22" s="9">
+        <v>250</v>
+      </c>
+      <c r="G22" s="9">
+        <v>5</v>
+      </c>
+      <c r="H22" s="9">
+        <v>450</v>
+      </c>
+      <c r="I22" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="10" t="str">
+        <v>1315</v>
+      </c>
+      <c r="J22" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="12"/>
+        <v>125</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N22" s="12" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="8"/>
